--- a/问题二/output/表1_指定日期购电量.xlsx
+++ b/问题二/output/表1_指定日期购电量.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>897.7349666666662</v>
+        <v>447.5766589615528</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>544.9558833333333</v>
+        <v>490.1940232273599</v>
       </c>
     </row>
     <row r="7">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>669.9064097332322</v>
       </c>
     </row>
     <row r="8">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>59917.15838868311</v>
+        <v>61828.33713717783</v>
       </c>
     </row>
     <row r="10">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>33230.70478526088</v>
+        <v>37796.99064040772</v>
       </c>
     </row>
   </sheetData>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>21.58518333333197</v>
+        <v>171.4387276481696</v>
       </c>
     </row>
     <row r="7">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>17644.77627119341</v>
+        <v>35344.3093850819</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7882.704820855286</v>
+        <v>20530.42249099871</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>501.9691666666668</v>
+        <v>468.0626007727482</v>
       </c>
     </row>
     <row r="5">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>559.5863833333333</v>
+        <v>560.4166474618627</v>
       </c>
     </row>
     <row r="7">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>770.5982453150131</v>
       </c>
     </row>
     <row r="8">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0</v>
+        <v>1.079193829063001</v>
       </c>
     </row>
     <row r="9">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>61993.34879999999</v>
+        <v>68616.55806703893</v>
       </c>
     </row>
     <row r="10">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>36461.88770027</v>
+        <v>43451.77751500752</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +797,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>196.2416460905369</v>
+        <v>808.8434465084481</v>
       </c>
     </row>
     <row r="5">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>825.4933383064993</v>
       </c>
     </row>
     <row r="7">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>700.7689130246854</v>
       </c>
     </row>
     <row r="8">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>26842.29554609054</v>
+        <v>96162.80329731983</v>
       </c>
     </row>
     <row r="10">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11374.0844408722</v>
+        <v>62369.91885031377</v>
       </c>
     </row>
   </sheetData>

--- a/问题二/output/表1_指定日期购电量.xlsx
+++ b/问题二/output/表1_指定日期购电量.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>669.9064097332322</v>
+        <v>679.0782107359005</v>
       </c>
     </row>
     <row r="8">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>61828.33713717783</v>
+        <v>62007.89364317169</v>
       </c>
     </row>
     <row r="10">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>37796.99064040772</v>
+        <v>37876.09291631295</v>
       </c>
     </row>
   </sheetData>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>35344.3093850819</v>
+        <v>33989.87423797375</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>20530.42249099871</v>
+        <v>19731.91686199551</v>
       </c>
     </row>
   </sheetData>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>68616.55806703893</v>
+        <v>65617.10974234402</v>
       </c>
     </row>
     <row r="10">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>43451.77751500752</v>
+        <v>41964.10972288273</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>825.4933383064993</v>
+        <v>822.0811702359363</v>
       </c>
     </row>
     <row r="7">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>96162.80329731983</v>
+        <v>96366.59398703404</v>
       </c>
     </row>
     <row r="10">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>62369.91885031377</v>
+        <v>62518.87338039021</v>
       </c>
     </row>
   </sheetData>
